--- a/api/templates/critical_errors_by_module/fr.xlsx
+++ b/api/templates/critical_errors_by_module/fr.xlsx
@@ -328,7 +328,7 @@
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>

--- a/api/templates/critical_errors_by_module/fr.xlsx
+++ b/api/templates/critical_errors_by_module/fr.xlsx
@@ -32,7 +32,7 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Dispositifs déclassés: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -328,7 +328,7 @@
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
